--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484039_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484039_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1233</v>
+        <v>2.9577</v>
       </c>
       <c r="E2" t="n">
-        <v>0.829</v>
+        <v>0.4209</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2943</v>
+        <v>2.5368</v>
       </c>
       <c r="G2" t="n">
         <v>0.3494</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>2.516</v>
+        <v>1.3504</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5839</v>
+        <v>0.1758</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9321</v>
+        <v>1.1746</v>
       </c>
       <c r="V2" t="n">
         <v>0.266</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0702</v>
+        <v>2.7361</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2945</v>
+        <v>2.9884</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2243</v>
+        <v>-0.2523</v>
       </c>
       <c r="G3" t="n">
         <v>2.1811</v>
@@ -688,13 +688,13 @@
         <v>2.3806</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7069</v>
+        <v>0.3727</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3856</v>
+        <v>0.0795</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3213</v>
+        <v>0.2933</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2065</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.581</v>
+        <v>1.7774</v>
       </c>
       <c r="E4" t="n">
         <v>1.9305</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3495</v>
+        <v>-0.1531</v>
       </c>
       <c r="G4" t="n">
         <v>3.501</v>
@@ -766,13 +766,13 @@
         <v>0.7935</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4767</v>
+        <v>0.6731</v>
       </c>
       <c r="T4" t="n">
         <v>0.5782</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1015</v>
+        <v>0.0949</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2065</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. BORRERO PERLAZA</t>
+          <t>A. CORTEGANO NAVARRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0363</v>
+        <v>0.5909</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5938</v>
+        <v>-1.4601</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5575</v>
+        <v>2.051</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0224</v>
+        <v>1.7623</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4686</v>
+        <v>-0.6293</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.491</v>
+        <v>2.3916</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1006</v>
+        <v>2.7232</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0605</v>
+        <v>-0.4521</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0402</v>
+        <v>3.1753</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.123</v>
+        <v>-0.9609</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4081</v>
+        <v>-0.1772</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5312</v>
+        <v>-0.7837</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3968</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.9677</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3968</v>
+        <v>2.579</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8683999999999999</v>
+        <v>-0.1913</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4932</v>
+        <v>-0.4817</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3752</v>
+        <v>0.2904</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2065</v>
+        <v>0.4085</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2065</v>
+        <v>0.1425</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. CORTEGANO NAVARRO</t>
+          <t>B. BORRERO PERLAZA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4779</v>
+        <v>-0.2341</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.2764</v>
+        <v>0.4918</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7985</v>
+        <v>-0.7259</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7623</v>
+        <v>-0.0224</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6293</v>
+        <v>0.4686</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3916</v>
+        <v>-0.491</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7232</v>
+        <v>0.1006</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4521</v>
+        <v>0.0605</v>
       </c>
       <c r="L6" t="n">
-        <v>3.1753</v>
+        <v>0.0402</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9609</v>
+        <v>-0.123</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1772</v>
+        <v>0.4081</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7837</v>
+        <v>-0.5312</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3887</v>
+        <v>0.3968</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.9677</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.579</v>
+        <v>0.3968</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.26</v>
+        <v>0.598</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2979</v>
+        <v>0.3911</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0379</v>
+        <v>0.2069</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4085</v>
+        <v>-1.2065</v>
       </c>
       <c r="W6" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1425</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. PUIG DE GRACIA</t>
+          <t>J. GAVALDA GUILLEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3019</v>
+        <v>-0.3565</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.293</v>
+        <v>-1.1418</v>
       </c>
       <c r="F7" t="n">
-        <v>2.991</v>
+        <v>0.7854</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.5423</v>
+        <v>-1.7013</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.3772</v>
+        <v>0.3574</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.1651</v>
+        <v>-2.0587</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.9814</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.6688</v>
+        <v>0.1411</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3126</v>
+        <v>-0.0701</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5609</v>
+        <v>-1.7723</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2916</v>
+        <v>0.2163</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8525</v>
+        <v>-1.9886</v>
       </c>
       <c r="P7" t="n">
-        <v>2.9758</v>
+        <v>1.3887</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9758</v>
+        <v>2.3806</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0844</v>
+        <v>-0.0439</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3116</v>
+        <v>-0.2209</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2272</v>
+        <v>0.1771</v>
       </c>
       <c r="V7" t="n">
-        <v>1.349</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.349</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GAVALDA GUILLEN</t>
+          <t>M. PUIG DE GRACIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4252</v>
+        <v>-1.6922</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9581</v>
+        <v>-4.5991</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5329</v>
+        <v>2.9069</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7013</v>
+        <v>-5.5423</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3574</v>
+        <v>-2.3772</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0587</v>
+        <v>-3.1651</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07099999999999999</v>
+        <v>-3.9814</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1411</v>
+        <v>-2.6688</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0701</v>
+        <v>-1.3126</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7723</v>
+        <v>-1.5609</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2163</v>
+        <v>0.2916</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9886</v>
+        <v>-1.8525</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3887</v>
+        <v>2.9758</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3806</v>
+        <v>2.9758</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1126</v>
+        <v>-0.4747</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0372</v>
+        <v>-0.6177</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.143</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.349</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.349</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. QUIROS LOPEZ</t>
+          <t>R. VERANO FORES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.072</v>
+        <v>-2.2501</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4954</v>
+        <v>-3.557</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4234</v>
+        <v>1.307</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8621</v>
+        <v>-2.3351</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9555</v>
+        <v>0.7808</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09329999999999999</v>
+        <v>-3.1159</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7586</v>
+        <v>-2.5595</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.839</v>
+        <v>0.1613</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0803</v>
+        <v>-2.7208</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1035</v>
+        <v>0.2244</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1165</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.013</v>
+        <v>-0.3951</v>
       </c>
       <c r="P9" t="n">
         <v>-0.1984</v>
@@ -1156,28 +1156,28 @@
         <v>0.7935</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2545</v>
+        <v>0.2834</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2551</v>
+        <v>-0.0056</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.289</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. BAJJA SANCHEZ</t>
+          <t>A. QUIROS LOPEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1225</v>
+        <v>-2.396</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7675</v>
+        <v>-2.9036</v>
       </c>
       <c r="F10" t="n">
-        <v>0.645</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5869</v>
+        <v>-1.8621</v>
       </c>
       <c r="H10" t="n">
-        <v>0.403</v>
+        <v>-1.9555</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.99</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5344</v>
+        <v>-1.7586</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6653</v>
+        <v>-1.839</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1997</v>
+        <v>0.0803</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0525</v>
+        <v>-0.1035</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2623</v>
+        <v>-0.1165</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7902</v>
+        <v>0.013</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5871</v>
+        <v>0.7935</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5357</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4252</v>
+        <v>-0.153</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1105</v>
+        <v>0.0835</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6745</v>
+        <v>-0.266</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5925</v>
+        <v>-2.6384</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1304</v>
+        <v>-2.2324</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4621</v>
+        <v>-0.406</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2016</v>
@@ -1312,13 +1312,13 @@
         <v>1.1903</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3945</v>
+        <v>0.3486</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2551</v>
+        <v>0.1531</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1394</v>
+        <v>0.1955</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. VERANO FORES</t>
+          <t>O. BAJJA SANCHEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9948</v>
+        <v>-2.6709</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9651</v>
+        <v>-3.1757</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.5047</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.3351</v>
+        <v>-1.5869</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7808</v>
+        <v>0.403</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.1159</v>
+        <v>-1.99</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.5595</v>
+        <v>-0.5344</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1613</v>
+        <v>0.6653</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.7208</v>
+        <v>-1.1997</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2244</v>
+        <v>-1.0525</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6195000000000001</v>
+        <v>-0.2623</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3951</v>
+        <v>-0.7902</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4614</v>
+        <v>-0.0127</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4137</v>
+        <v>0.0171</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0476</v>
+        <v>-0.0298</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.176</v>
+        <v>-4.176100000000002</v>
       </c>
       <c r="E13" t="n">
         <v>-13.2381</v>
       </c>
       <c r="F13" t="n">
-        <v>9.061999999999999</v>
+        <v>9.062099999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.4579</v>
+        <v>-6.457899999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0815</v>
+        <v>-1.081499999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.3766</v>
+        <v>-5.376600000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>2.593100000000001</v>
+        <v>2.593099999999999</v>
       </c>
       <c r="K13" t="n">
         <v>-1.908200000000001</v>
@@ -1453,13 +1453,13 @@
         <v>-9.0509</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8267000000000001</v>
+        <v>0.8267</v>
       </c>
       <c r="O13" t="n">
         <v>-9.877800000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>1.983800000000001</v>
+        <v>1.9838</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.8706</v>
@@ -1468,13 +1468,13 @@
         <v>17.8545</v>
       </c>
       <c r="S13" t="n">
-        <v>2.834299999999999</v>
+        <v>2.8341</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.08409999999999979</v>
+        <v>-0.08409999999999995</v>
       </c>
       <c r="U13" t="n">
-        <v>2.9185</v>
+        <v>2.9184</v>
       </c>
       <c r="V13" t="n">
         <v>-2.5365</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MARTIN MONZON</t>
+          <t>J. ROSA DE SOU DA SIL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1997</v>
+        <v>5.0231</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8164</v>
+        <v>3.0361</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3833</v>
+        <v>1.987</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4288</v>
+        <v>5.1578</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5692</v>
+        <v>1.8439</v>
       </c>
       <c r="I14" t="n">
-        <v>2.998</v>
+        <v>3.3139</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4179</v>
+        <v>4.5551</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.4803</v>
+        <v>1.0081</v>
       </c>
       <c r="L14" t="n">
-        <v>3.8982</v>
+        <v>3.547</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0109</v>
+        <v>0.6027</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9111</v>
+        <v>0.8358</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9003</v>
+        <v>-0.2331</v>
       </c>
       <c r="P14" t="n">
         <v>0.3968</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3806</v>
+        <v>1.3887</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1677</v>
+        <v>-0.5314</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1758</v>
+        <v>-0.5271</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0081</v>
+        <v>-0.0044</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. ROSA DE SOU DA SIL</t>
+          <t>J. MARTIN MONZON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0904</v>
+        <v>4.0773</v>
       </c>
       <c r="E15" t="n">
-        <v>2.628</v>
+        <v>1.5103</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4624</v>
+        <v>2.567</v>
       </c>
       <c r="G15" t="n">
-        <v>5.1578</v>
+        <v>2.4288</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8439</v>
+        <v>-0.5692</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3139</v>
+        <v>2.998</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5551</v>
+        <v>2.4179</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0081</v>
+        <v>-1.4803</v>
       </c>
       <c r="L15" t="n">
-        <v>3.547</v>
+        <v>3.8982</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6027</v>
+        <v>0.0109</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8358</v>
+        <v>0.9111</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2331</v>
+        <v>-0.9003</v>
       </c>
       <c r="P15" t="n">
         <v>0.3968</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3887</v>
+        <v>2.3806</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4641</v>
+        <v>0.0453</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9352</v>
+        <v>-0.1303</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.529</v>
+        <v>0.1755</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MEDORI MORALES</t>
+          <t>L. MARTINEZ YRANZO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7428</v>
+        <v>2.7755</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1012</v>
+        <v>0.9745</v>
       </c>
       <c r="F16" t="n">
-        <v>2.844</v>
+        <v>1.801</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6929999999999999</v>
+        <v>2.0513</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0535</v>
+        <v>1.8997</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7465</v>
+        <v>0.1516</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9688</v>
+        <v>2.5911</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6845</v>
+        <v>1.2606</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6532</v>
+        <v>1.3304</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2758</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.369</v>
+        <v>0.639</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-1.1788</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1903</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.9677</v>
+        <v>-1.9838</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7774</v>
+        <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7082</v>
+        <v>0.1247</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0998</v>
+        <v>-0.4307</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6084</v>
+        <v>0.5554</v>
       </c>
       <c r="V16" t="n">
-        <v>0.532</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="W16" t="n">
         <v>0.7979000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. MARTINEZ YRANZO</t>
+          <t>D. COFFIE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1023</v>
+        <v>1.5527</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1582</v>
+        <v>-0.3375</v>
       </c>
       <c r="F17" t="n">
-        <v>0.944</v>
+        <v>1.8902</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0513</v>
+        <v>1.7298</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8997</v>
+        <v>0.2464</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1516</v>
+        <v>1.4834</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5911</v>
+        <v>2.094</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2606</v>
+        <v>0.0859</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3304</v>
+        <v>2.0081</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.3642</v>
       </c>
       <c r="N17" t="n">
-        <v>0.639</v>
+        <v>0.1605</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1788</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7855</v>
+        <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5485</v>
+        <v>-0.1771</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2469</v>
+        <v>-0.4477</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3016</v>
+        <v>0.2706</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7979000000000001</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7979000000000001</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. COFFIE</t>
+          <t>J. MEDORI MORALES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6081</v>
+        <v>0.9727</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9497</v>
+        <v>-1.3255</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5578</v>
+        <v>2.2982</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7298</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2464</v>
+        <v>-1.0535</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4834</v>
+        <v>1.7465</v>
       </c>
       <c r="J18" t="n">
-        <v>2.094</v>
+        <v>1.9688</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0859</v>
+        <v>-0.6845</v>
       </c>
       <c r="L18" t="n">
-        <v>2.0081</v>
+        <v>2.6532</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3642</v>
+        <v>-1.2758</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1605</v>
+        <v>-0.369</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.9068000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9838</v>
+        <v>-3.9677</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9838</v>
+        <v>2.7774</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1217</v>
+        <v>0.9381</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0599</v>
+        <v>-0.1245</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0619</v>
+        <v>1.0626</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CASTILLO EDIO</t>
+          <t>P. GUASCH BENLLOCH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0363</v>
+        <v>0.0062</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5437</v>
+        <v>-0.1669</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5074</v>
+        <v>0.1731</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8848</v>
+        <v>0.3676</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5495</v>
+        <v>-0.0405</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.4343</v>
+        <v>0.4081</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9369</v>
+        <v>0.0202</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1825</v>
+        <v>0.0202</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1194</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9479</v>
+        <v>0.3474</v>
       </c>
       <c r="N19" t="n">
-        <v>0.367</v>
+        <v>-0.0607</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3149</v>
+        <v>0.4081</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7935</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7855</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4635</v>
+        <v>-0.3614</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7937</v>
+        <v>-0.187</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6698</v>
+        <v>-0.1743</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. GUASCH BENLLOCH</t>
+          <t>A. CASTILLO EDIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.134</v>
+        <v>-0.7488</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1669</v>
+        <v>-2.3599</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0328</v>
+        <v>1.6111</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3676</v>
+        <v>-1.8848</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0405</v>
+        <v>0.5495</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4081</v>
+        <v>-2.4343</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0202</v>
+        <v>-0.9369</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0202</v>
+        <v>0.1825</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.1194</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3474</v>
+        <v>-0.9479</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0607</v>
+        <v>0.367</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4081</v>
+        <v>-1.3149</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.7935</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.7855</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5016</v>
+        <v>0.751</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.187</v>
+        <v>-0.0226</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3146</v>
+        <v>0.7736</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.4085</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.4085</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2799</v>
+        <v>-0.8556</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0523</v>
+        <v>-1.8482</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7724</v>
+        <v>0.9926</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9566</v>
@@ -2092,13 +2092,13 @@
         <v>1.9838</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0492</v>
+        <v>-0.6249</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5611</v>
+        <v>-0.357</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.488</v>
+        <v>-0.2678</v>
       </c>
       <c r="V21" t="n">
         <v>-0.266</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7001</v>
+        <v>-2.5878</v>
       </c>
       <c r="E22" t="n">
         <v>-2.1106</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5895</v>
+        <v>-0.4773</v>
       </c>
       <c r="G22" t="n">
         <v>0.2061</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6564</v>
+        <v>-0.5442</v>
       </c>
       <c r="T22" t="n">
         <v>-0.187</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4693</v>
+        <v>-0.3571</v>
       </c>
       <c r="V22" t="n">
         <v>-0.266</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4168</v>
+        <v>-3.9985</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.7403</v>
+        <v>-6.4342</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3235</v>
+        <v>2.4357</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3349</v>
@@ -2248,13 +2248,13 @@
         <v>1.7855</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8321</v>
+        <v>-0.4138</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8105</v>
+        <v>-0.5044</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0216</v>
+        <v>0.0906</v>
       </c>
       <c r="V23" t="n">
         <v>0.9405</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4.1762</v>
+        <v>6.216799999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.062100000000001</v>
+        <v>-9.061899999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>13.2381</v>
+        <v>15.2786</v>
       </c>
       <c r="G24" t="n">
         <v>6.458099999999999</v>
@@ -2302,7 +2302,7 @@
         <v>9.051300000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8267000000000001</v>
+        <v>-0.8267</v>
       </c>
       <c r="L24" t="n">
         <v>9.8779</v>
@@ -2314,7 +2314,7 @@
         <v>1.9082</v>
       </c>
       <c r="O24" t="n">
-        <v>-4.5014</v>
+        <v>-4.501399999999999</v>
       </c>
       <c r="P24" t="n">
         <v>-1.9838</v>
@@ -2326,13 +2326,13 @@
         <v>15.8708</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.8342</v>
+        <v>-0.7937000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.918299999999999</v>
+        <v>-2.9183</v>
       </c>
       <c r="U24" t="n">
-        <v>0.08409999999999995</v>
+        <v>2.1247</v>
       </c>
       <c r="V24" t="n">
         <v>2.5364</v>
